--- a/demo 4 (alpha interpolated)/Pb210_results/CFCS modeling data/MAR_model_summaries.xlsx
+++ b/demo 4 (alpha interpolated)/Pb210_results/CFCS modeling data/MAR_model_summaries.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>2.521698953312942</v>
+        <v>2.521170458878704</v>
       </c>
       <c r="D2">
-        <v>0.04926586372687492</v>
+        <v>0.04936926780628167</v>
       </c>
       <c r="E2">
-        <v>51.18552203393797</v>
+        <v>51.06760887707379</v>
       </c>
       <c r="F2">
-        <v>1.239780932238842E-27</v>
+        <v>1.315647592206131E-27</v>
       </c>
       <c r="G2">
-        <v>0.9422619544318293</v>
+        <v>0.9423363127409601</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.2273580612273553</v>
+        <v>-0.2279907568934243</v>
       </c>
       <c r="D3">
-        <v>0.01081885831544878</v>
+        <v>0.01084156600795049</v>
       </c>
       <c r="E3">
-        <v>-21.01497723680323</v>
+        <v>-21.02931963207446</v>
       </c>
       <c r="F3">
-        <v>7.721883921092865E-18</v>
+        <v>7.593331091049281E-18</v>
       </c>
       <c r="G3">
-        <v>0.9422619544318293</v>
+        <v>0.9423363127409601</v>
       </c>
     </row>
     <row r="4">
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>5.7181211704731</v>
+        <v>5.780087268463749</v>
       </c>
       <c r="D4">
-        <v>0.3658663737269559</v>
+        <v>0.3712765924916193</v>
       </c>
       <c r="E4">
-        <v>15.62898801610148</v>
+        <v>15.56814349559142</v>
       </c>
       <c r="F4">
-        <v>4.345559493162324E-06</v>
+        <v>4.446268928192789E-06</v>
       </c>
       <c r="G4">
-        <v>0.9714823929119137</v>
+        <v>0.97140772488803</v>
       </c>
     </row>
     <row r="5">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.6261707906785711</v>
+        <v>-0.6345791751314133</v>
       </c>
       <c r="D5">
-        <v>0.04046449720400423</v>
+        <v>0.04106286261224247</v>
       </c>
       <c r="E5">
-        <v>-15.4745723769084</v>
+        <v>-15.45384648712289</v>
       </c>
       <c r="F5">
-        <v>4.606494085374722E-06</v>
+        <v>4.642886368475381E-06</v>
       </c>
       <c r="G5">
-        <v>0.9714823929119137</v>
+        <v>0.97140772488803</v>
       </c>
     </row>
   </sheetData>
